--- a/source/人工智能场景计划表-0809.xlsx
+++ b/source/人工智能场景计划表-0809.xlsx
@@ -2387,8 +2387,8 @@
       <c r="D14" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="E14" s="12" t="s">
-        <v>24</v>
+      <c r="E14" s="14" t="s">
+        <v>18</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>25</v>
@@ -2427,8 +2427,8 @@
       <c r="D15" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="E15" s="12" t="s">
-        <v>24</v>
+      <c r="E15" s="14" t="s">
+        <v>18</v>
       </c>
       <c r="F15" s="13" t="s">
         <v>25</v>
@@ -2467,8 +2467,8 @@
       <c r="D16" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="E16" s="12" t="s">
-        <v>24</v>
+      <c r="E16" s="14" t="s">
+        <v>18</v>
       </c>
       <c r="F16" s="13">
         <v>46234</v>
@@ -2879,8 +2879,8 @@
       <c r="D27" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="E27" s="12" t="s">
-        <v>24</v>
+      <c r="E27" s="14" t="s">
+        <v>18</v>
       </c>
       <c r="F27" s="13">
         <v>46233</v>
@@ -3043,8 +3043,8 @@
       <c r="D31" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="E31" s="12" t="s">
-        <v>18</v>
+      <c r="E31" s="14" t="s">
+        <v>24</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>25</v>
@@ -3083,8 +3083,8 @@
       <c r="D32" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="E32" s="12" t="s">
-        <v>24</v>
+      <c r="E32" s="14" t="s">
+        <v>18</v>
       </c>
       <c r="F32" s="13">
         <v>46234</v>
@@ -3123,8 +3123,8 @@
       <c r="D33" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="E33" s="12" t="s">
-        <v>24</v>
+      <c r="E33" s="14" t="s">
+        <v>18</v>
       </c>
       <c r="F33" s="13">
         <v>46234</v>
@@ -3527,7 +3527,7 @@
       <c r="D43" s="28" t="s">
         <v>120</v>
       </c>
-      <c r="E43" s="12" t="s">
+      <c r="E43" s="14" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="13" t="s">
@@ -3567,8 +3567,8 @@
       <c r="D44" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="E44" s="12" t="s">
-        <v>19</v>
+      <c r="E44" s="14" t="s">
+        <v>18</v>
       </c>
       <c r="F44" s="13" t="s">
         <v>123</v>
@@ -3755,8 +3755,8 @@
       <c r="D49" s="28" t="s">
         <v>134</v>
       </c>
-      <c r="E49" s="12" t="s">
-        <v>19</v>
+      <c r="E49" s="14" t="s">
+        <v>18</v>
       </c>
       <c r="F49" s="13" t="s">
         <v>135</v>
@@ -3795,8 +3795,8 @@
       <c r="D50" s="28" t="s">
         <v>137</v>
       </c>
-      <c r="E50" s="12" t="s">
-        <v>19</v>
+      <c r="E50" s="14" t="s">
+        <v>18</v>
       </c>
       <c r="F50" s="13" t="s">
         <v>135</v>
@@ -3899,8 +3899,8 @@
       <c r="D53" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="E53" s="12" t="s">
-        <v>19</v>
+      <c r="E53" s="14" t="s">
+        <v>24</v>
       </c>
       <c r="F53" s="13" t="s">
         <v>135</v>
@@ -4147,8 +4147,8 @@
       <c r="D59" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="E59" s="12" t="s">
-        <v>24</v>
+      <c r="E59" s="14" t="s">
+        <v>18</v>
       </c>
       <c r="F59" s="13">
         <v>46234</v>
@@ -4931,8 +4931,8 @@
       <c r="D79" s="12" t="s">
         <v>186</v>
       </c>
-      <c r="E79" s="12" t="s">
-        <v>24</v>
+      <c r="E79" s="14" t="s">
+        <v>18</v>
       </c>
       <c r="F79" s="13">
         <v>46241</v>
